--- a/Excel/Common_v02.prename.bak.xlsx
+++ b/Excel/Common_v02.prename.bak.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD6DD20-F011-445D-B09A-D8B6120FF91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1AC07D-9708-4868-9B33-546D05014869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="1125" windowWidth="37140" windowHeight="20475" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
-    <sheet name="Constants - Common" sheetId="2" r:id="rId2"/>
+    <sheet name="Constants - Common" sheetId="5" r:id="rId2"/>
     <sheet name="Acknowledgements" sheetId="4" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -173,11 +176,15 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="1">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="1">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="1">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -189,7 +196,9 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="1">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="1">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -2211,6 +2220,26 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -2276,20 +2305,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D55AFDDE-E44E-4566-9446-49D22D1085DF}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{12C80AD8-6332-49FA-A3BC-E6FC90290331}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8BD56FF8-29E2-4DF7-85A1-55618F035A34}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{9A129CA1-FCF6-4181-AD59-C31782B90B45}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F5DA0D0E-6BC4-4950-A99F-5113C027644B}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{48D3DF45-3A54-423E-A5F3-9494AB3064B3}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{387B7C9E-D7D9-4D36-A290-1A81ACD3515A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{7DA5D9C6-D776-4FCA-A8D8-84EBABC8BB93}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2298,16 +2327,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{1BFC15E8-D67C-4277-8EF9-438444043863}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{921941D7-3BE7-471F-99BE-83856E582E55}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{59A3EF04-81A1-4788-92ED-C93EB4567386}" name="Data source">
+    <tableColumn id="1" xr3:uid="{55A138C7-E5D5-4DF5-92E5-A7FD2B8C0774}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{08331E38-C96C-45D2-ABE0-F9E96883DAB0}" name="Data score">
+    <tableColumn id="2" xr3:uid="{6B6251B8-1F75-43F6-806F-F938323943B9}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2316,16 +2345,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{D871F994-12EC-4014-A3F3-C7F599044252}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{99A6D084-0703-4C94-B11D-4C23517634DE}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CA74DB79-CAE7-4EF8-BA48-96421E9E9373}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{A044B3E4-231A-497F-8D52-B9A7A3DFF13F}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0DDE0C3-8378-485B-A4A4-D07B38ADF801}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{01FE0B6B-8CAE-4C77-91C6-4119EF6A37DC}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2334,7 +2363,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{CFF24A4D-FB3A-4990-A60E-B22F27A25574}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{10A28533-75BD-41BD-815D-334C8EC9A5A3}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2343,19 +2372,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{849A0981-50FD-4A56-9339-1D4877F4BC58}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{27A07D70-72BC-4CFD-89CC-630D7F72EE04}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{956974C7-4464-4357-8D9E-FC82DB381483}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{8E636884-2575-4D9C-8515-07877480E93E}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{31E180E3-1F8B-483C-A30C-1675039A95CA}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{3F790367-A7ED-4BA4-B5CF-85F3B4818887}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C9763E21-E4AE-4087-BDBD-60136B5D44A0}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{BFDC0148-E0BB-4540-9E4A-FAC9267A4EED}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3490D434-A455-4128-8D9F-A4C3B5BCB722}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{E0691405-E450-4ADE-A1F7-BF47621250F9}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2364,16 +2393,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{AAECC632-9B06-47A4-BC48-EA3475DCA70D}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B18D772B-2FE9-457A-A200-8E17C55C340C}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{34FE5461-39F9-4C52-82B8-8DDCADF8EC64}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A11A4C1D-EDEC-4818-93B7-672872C6D107}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{523507B8-C845-462F-A46F-B27B83A8E3E4}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2382,16 +2411,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{B52031B6-1284-42FC-BB5D-A52450C47E85}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{718360C9-DDF8-4B7B-B842-EE0D39ED743F}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{F3E9CDB4-673B-4442-979D-53DD754D6F7B}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{876E0F1A-E7CF-4E69-9C3F-6E0E84FF4B5D}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B7ED561D-79EF-44FD-AB5A-3AD1FDF43AF4}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2400,16 +2429,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{AB3534A6-83C2-421B-88FF-1793AEB2A759}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7CBE043C-4D22-47C3-AE18-5E55E64542E1}" name="Month">
+    <tableColumn id="1" xr3:uid="{38533537-B6FC-4DE6-A910-1C59DE183195}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{10DA8C9D-4358-470A-AF6C-AE27470313DE}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5903A14B-CD3F-4C70-939F-0C38887997C7}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2418,7 +2447,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{0CD50652-F828-4BAC-92D9-3A6D74FFE2E1}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2438,52 +2467,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8E03AF9F-C6DD-415E-A42C-F2360BC32F72}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{5FAAF41E-314C-4573-9CA4-6C8EABFC1195}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{07B3EB32-B4EC-4553-A2E1-8AE19F5ED1B8}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B7311E91-C430-4320-A137-B8FA34BE281D}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D245CE73-83DF-4AB6-BE51-10D787832614}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{4677D10F-8319-45F2-AA1A-3EC1241F49F2}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96977D75-8628-4103-9D52-F7049CB2572B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{BC251906-2264-4995-9FD9-A4AA0EC14B59}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F64B281A-2EA4-4881-94F1-FEBD2B18C677}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{3DBAC453-EF7E-487F-B91B-57F676B72346}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8934BA44-DDF5-433B-A89F-5DB281BAB7B5}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{F06FC22B-292E-425D-B5F1-CBCD5D92D153}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{699EC0ED-651C-48B9-9F8F-73146B12DB72}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{913B2A8F-0AF6-4A9D-AFFD-4D8471FEE2E4}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6E240578-9A8B-47C9-A356-B69BB058D44B}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{6105389B-21E1-40CE-B388-B8BA7E5B3234}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{922DD34E-8EDF-42D6-BE68-8D30A5F4A8CF}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{14D7C4D1-8181-4528-85DE-A511754B9482}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{730FA508-F44F-43A0-8A87-F28C2DB6D4D5}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{67D740BF-25DF-45EE-82E5-A26830CAED11}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8BD6E90D-D2CF-4733-8286-F67C28172389}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8255E427-B0B1-47DD-B7EE-389455146B66}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE74F5BC-4374-40FF-85F0-AE26E403B07E}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{97EF86FB-EB3B-484D-BEB8-DED533845ECE}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B53034D9-4966-41B7-BD99-44BBB861677D}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{27A6DE7F-0F1E-4957-ACC5-8981DE32AD72}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{59F06DF1-1149-43CE-9ADC-FD2C1D44B8D0}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{6CAA147D-A40B-48BF-8F15-65FDCA87C950}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E8CF9642-D223-420C-B387-277C82D3BB2E}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{EF20BA7B-5A8B-4E38-AAB0-4A9CCCE7EB93}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0B403FCE-8D29-4E28-99ED-B0004709790F}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{C12A23DC-0942-4C2B-BCCA-3789024FE991}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2492,16 +2521,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{13892DA7-3EC5-4525-9CE2-44E4C44DA522}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3C12381E-3675-4A77-B50C-CAF33F1781C7}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{418FE0BA-8A91-457F-BBD7-90E45418FBEF}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{15B1FB4A-EB78-4095-8978-98D149B427BD}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{25BE8AC2-31E8-4D4A-ADDA-F1B134F0ED6E}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2510,12 +2539,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B68A2510-6801-4CC4-A35D-1182F8B5B0D6}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{BA3484FA-C1AF-436A-8651-4D9AAA48D0E0}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FEC43FAA-C4DB-43B0-B971-1FF71C5C3EB9}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{4D648E8B-D0ED-48D9-9E5D-E98BA288914E}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2524,16 +2553,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A8693B4F-0827-4BC0-8BFF-4E2F8802A9A6}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{2A1D02B5-CFE6-4892-BA5C-DC2801F766EF}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{58198B4B-31B9-425F-A0C1-D1593EEF16FC}" name="Gas">
+    <tableColumn id="1" xr3:uid="{E0A494C8-CF2B-4C96-9A7B-5EB3CD28A421}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B9F0B86C-9146-4976-B742-C78D7C3C1146}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{DEC7626E-8CAE-4238-8CE4-0112C5BCD2F9}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2542,7 +2571,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62FC099-DF5F-42B5-806A-E7A932074694}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{04A63D28-6347-4626-AA52-97635191032D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2551,19 +2580,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A6E029C1-D4D4-46E4-9D9D-9AA604F09519}" name="Gas">
+    <tableColumn id="1" xr3:uid="{35F6146A-A67B-434F-8D6B-F001EB28A552}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{AD8A597E-16A3-42B7-A64E-7A1DF4ED3338}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{36FB3C35-4C6D-4852-A1C5-8CA82F63DB5D}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FB88E96D-D31C-4C55-BB92-4DA916E3D9DA}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{14E43155-E0FF-49E9-BB08-A4DED380B7B4}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B708733D-F7A9-4A74-8BE2-FF67131886D8}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{AC6141BE-9B80-4E6A-A961-11178804BCF6}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D26A421E-E754-4C8A-9D08-12DF73D61E7C}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{143B46A0-49EF-4B5D-8C7A-16D1503E1A0B}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2572,7 +2601,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFF0180F-7F7D-4433-BEE0-8A0A823637BF}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{AB8342F1-2993-4F09-8525-7EA1A78DB177}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2592,52 +2621,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{8938BBE8-7B92-48A9-872B-3320D21DB635}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C8318248-5646-48AA-8D73-3250AF8C3755}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{658207C9-89A7-4F8D-BFB1-8E32C6E5CE10}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B43C74B2-D7C9-4E6A-969E-D8995C899E1F}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{354F10CE-DC7A-49A5-AA19-EEB6281A6412}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{4506B4D8-CF82-4F3A-83D5-2CB373B9ACB3}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38F4182B-B4B5-426D-98BC-0B2593A7B2AC}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{A228B3CF-7386-46AC-94B6-4F6ECB43B42F}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EE15735E-8ABF-428C-B015-3F1955A6D060}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{94688278-C780-4018-91CE-BF28E7EC4D8B}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{24D889BF-3FFC-47F8-87FE-E95F033D2601}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{433F4C36-F6FC-47DB-B372-AF2C1342219F}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B1AA507-6E86-4E0A-8123-6045EBFC43F0}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{3AD621D8-B8E3-4A03-9412-D3BF8AA60BDC}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B7A64A9C-167B-48BE-9126-A0FC1AEC24A5}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{DBDBD834-E45A-42B1-A2F3-EA3A0EC62F93}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6A8CA332-9832-49EA-97FB-DD23C730245E}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{D8CDE8F0-1C94-4E96-BA0A-751FFEC10EEC}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B24E0786-86EC-449C-85EE-60C753B18536}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{22B5E358-1A2A-4B37-970D-4AC483F9C548}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{25C5B38E-3202-4F57-A055-5B1AD8BE4CEF}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{4D39EE6E-8AF0-4C65-8128-C27ECB22009E}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E486BEC3-9016-4BF3-8FB0-8F4450C55190}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E7A86A47-EC19-41A8-B564-597FD51684B9}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8C9D6103-6384-43E4-AD6A-556A38AB52A4}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{892DA7AD-9168-4563-BC97-1385B57FC980}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BF7FD137-AA7E-444B-8D18-DC8AB8FE4C1A}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{A0B9B1FD-B236-474E-9122-15E12864CF5D}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{99EBF2EA-96A6-4345-93B0-3364616813EA}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{F8755ED4-9579-4EEA-8A4A-AE101D51E5A4}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3EB0AAD6-2B47-4B1F-AB9F-DF46F10D5123}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{91D17622-B40E-4361-80D2-D1988DDFC370}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2646,16 +2675,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{332A6A92-FC29-4D50-BA04-0826843E7703}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B11B19BC-8665-4DB0-A415-A517CC19509B}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2FCD4A06-823B-4A3F-89D0-46C27A9E1AA9}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{12904C09-DA4D-412E-8E03-AB328814AB38}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{605D6DF8-71A8-491A-BF4E-F6D008835D65}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C2A46A32-DB7A-4A6C-99C4-AB4E8A95293D}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2664,7 +2693,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F9FC6E4B-1485-47B3-B981-452B30BCE51E}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{925C1D97-3C1F-4BF7-A4D5-D8E048C3D41F}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2672,16 +2701,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5FDD3467-EE45-473F-B48C-CD61900185F2}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{C2062EB9-8BCE-4CC3-B63A-E51C19A3A6B2}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3152390A-DC85-4607-A3A6-0AA517B5C99A}" name="MAT">
+    <tableColumn id="2" xr3:uid="{F08A3367-FC4F-42AC-8EE2-DCEA5BC7DD7B}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0ADEDEE0-6AD4-4B94-BBD5-BCBB07E1B11F}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{605A1120-3D5B-433A-BE51-A4951A383637}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{865B2916-F18A-4E99-BE24-FAB9BFD4F68A}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{01775834-9014-4037-8C7C-70490C991A3E}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2690,7 +2719,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B7337C26-229C-4E09-A297-90C453C060F3}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{9752A569-EEA8-4C71-808F-511E500CFD0D}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2698,16 +2727,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9AEEFC53-E611-4230-AAAF-3DE6B5E5E950}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{8B246171-EE1D-4160-AC12-5E898FD4B117}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C472DBB4-6A9E-4914-AA99-450142F197F5}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{8F3A56EB-6EE3-48E3-BEF1-878AB4DD860B}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0286587B-B8A4-411F-86B6-7742963B61A7}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{9A43D887-0470-4AAB-B168-E3272114B329}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9A50E08F-C1E5-4577-BFCD-3512C380DD34}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{399F7227-D718-4CC8-8661-7668F5975B12}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2716,16 +2745,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{7DB7A349-D3DD-4014-9714-0EE906A80983}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{AC212825-7AF1-49C1-94D4-CD799060BF73}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61D54A58-B9CE-4F4F-A6C1-9709184F0C68}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{D5C7FE71-1BB0-47EF-BF35-1337DFD309B3}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FA4910CF-D781-41C4-A05F-986A4A73D67B}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{1BFB5620-95C2-49E3-BF2F-39ED90B9138B}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3002,7 +3031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83968956-F921-4291-AAEE-DE11952DD430}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2339B39-A232-46C5-ACDC-974257207825}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7009,6 +7038,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -7203,31 +7256,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7244,31 +7300,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/Common_v02.prename.bak.xlsx
+++ b/Excel/Common_v02.prename.bak.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1AC07D-9708-4868-9B33-546D05014869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5318154-DEDA-4DF1-9142-42C8225BA0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="3" r:id="rId1"/>
     <sheet name="Constants - Common" sheetId="5" r:id="rId2"/>
     <sheet name="Acknowledgements" sheetId="4" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -35,7 +32,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -51,9 +58,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -2220,26 +2246,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -7038,30 +7044,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -7256,34 +7238,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUATgAyAE8AIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBOADIATwA6ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcAG4ARwBXAFAATgAyAE8AOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABHAFcAUABfAE4AMgBPACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKgAgAEcAVwBQAF8ATgAyAE8AXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsATgAyAE8AfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsATgAyAE8AfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAE4AMgBPAFwAIgAsAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXABuAEUAQwBIADQAIABDAE8AMgBlAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBDAEgANAA6ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcAG4ARwBXAFAAQwBIADQAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAEMASAA0ACwAIABHAFcAUABfAEMASAA0ACwAXABuACAAIAAgACAARQBfAEMASAA0ACAAKgAgAEcAVwBQAF8AQwBIADQAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAE8AMgBfAGUAIAA9ACAARQBfAHsAQwBIADQAfQAgAFwAXAB0AGkAbQBlAHMAIABHAFcAUABfAHsAQwBIADQAfQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMASAA0AFwAIgAsAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABDAEgANABcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7300,4 +7279,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>